--- a/PNC_Showroom_Inventory_Tracker.xlsx
+++ b/PNC_Showroom_Inventory_Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pncorp-my.sharepoint.com/personal/bent_pncorp_com/Documents/Desktop/Showroom Inventory/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pncorp-my.sharepoint.com/personal/bent_pncorp_com/Documents/Desktop/Showroom Inventory/piedmont-showroom-prototype/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{B9399D65-3203-4713-B00C-14B8B86699B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702BC33F-7B74-43F9-A4D6-DDC036C4F719}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{B9399D65-3203-4713-B00C-14B8B86699B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1350561B-6D53-457D-92A7-FDE354A896F4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
   <si>
     <t>Piedmont Showroom Equipment — Inventory Template</t>
   </si>
@@ -264,7 +264,13 @@
     <t>4" Wide Print Direct on Bag</t>
   </si>
   <si>
-    <t>C:\Users\bent.PNC\OneDrive - PNC\Desktop\Showroom Inventory\sharp-sx.jpg</t>
+    <t>sharp-sx.jpg</t>
+  </si>
+  <si>
+    <t>texwrap-tls-2219.jpg</t>
+  </si>
+  <si>
+    <t>garrido-601-l-bar-sealer.jpg</t>
   </si>
 </sst>
 </file>
@@ -516,6 +522,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -908,7 +918,9 @@
       <c r="O8" s="17">
         <v>1</v>
       </c>
-      <c r="P8" s="15"/>
+      <c r="P8" t="s">
+        <v>76</v>
+      </c>
       <c r="Q8" s="18" t="str">
         <f t="shared" si="0"/>
         <v>YES</v>
@@ -965,7 +977,9 @@
       <c r="O9" s="17">
         <v>1</v>
       </c>
-      <c r="P9" s="15"/>
+      <c r="P9" s="15" t="s">
+        <v>77</v>
+      </c>
       <c r="Q9" s="18" t="str">
         <f t="shared" si="0"/>
         <v>YES</v>
